--- a/dashboard/apra_forecast_input_template.xlsx
+++ b/dashboard/apra_forecast_input_template.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Shipments" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Price" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Weather" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -467,163 +469,163 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Fill in the "Data" sheet with your own shipment data, then upload it when</t>
+          <t>This workbook has three data sheets: Shipments (required), Price and</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>starting a new scenario run. This file replaces the default dataset for that run.</t>
+          <t>Weather (both optional). Fill in what you have and upload the whole file</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>when starting a new scenario run — it replaces the default dataset for</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Required columns</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>that run only.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ship_day        Date of the shipment, e.g. 2025-06-01 (any standard date format is fine).</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  asin            Product identifier (any string — SKU code, ASIN, etc).</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shipments sheet (required)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  postal_code     Destination postal/zip code as text (e.g. 135-0061).</t>
+          <t xml:space="preserve">  ship_day        Date of the shipment, e.g. 2025-06-01 (any standard date format).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  asin            Product identifier (any string — SKU code, ASIN, etc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  postal_code     Destination postal/zip code as text (e.g. 135-0061).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  shipped_units   Units shipped that day for that product/postal_code (positive number).</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Optional columns (improve accuracy if included)</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  avg_our_price      Average selling price for that row.</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  avg_discount_amt   Average discount applied for that row.</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Price sheet (optional)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ship_day, asin       Same meaning as in Shipments — used to match price to shipments.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Past-looking vs. future-looking data</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  avg_our_price        Average selling price for that product/day.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  This is ONE combined file — the model automatically splits it by date:</t>
+          <t xml:space="preserve">  avg_discount_amt     Average discount applied for that product/day.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Rows with earlier dates are used to TRAIN the model.</t>
+          <t xml:space="preserve">  If your price varies by postal_code too, add a postal_code column here</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The most recent ~20% of dates (by default) are held out as a BACKTEST —</t>
+          <t xml:space="preserve">  and it will be matched at that finer level instead.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    the model predicts those dates and compares against your real shipped_units</t>
+          <t xml:space="preserve">  Leave this sheet empty and the model simply runs without price features</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    to measure accuracy, so include real historical actuals through as recent a</t>
+          <t xml:space="preserve">  (the platform default when no price signal is supplied).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    date as you have them.</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The forecast automatically extends ~8 weeks beyond the LAST date in your</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Weather sheet (optional)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    file — that forward projection has no actuals yet, which is expected.</t>
+          <t xml:space="preserve">  postal_code, ship_day   Same meaning as in Shipments.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  In short: upload purely historical data for a standard backtest, or include</t>
+          <t xml:space="preserve">  temp_mean, temp_max, temp_min, precip_mm, is_hot, is_cold</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  it all the way through the present for the freshest possible forward forecast.</t>
+          <t xml:space="preserve">  Leave this sheet empty and the platform's own default weather data is used</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  There is no separate "future file" — just include every date you have.</t>
+          <t xml:space="preserve">  instead (only relevant if the "Weather signal" option is on for the run).</t>
         </is>
       </c>
     </row>
@@ -633,38 +635,153 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Minimum size</t>
+          <t>Past-looking vs. future-looking data</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  At least ~20 distinct dates of history are required to train and backtest.</t>
+          <t xml:space="preserve">  The Shipments sheet is ONE combined file — the model automatically splits</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  More history (6-12+ months) will generally produce a more reliable model.</t>
+          <t xml:space="preserve">  it by date:</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Earlier dates are used to TRAIN the model.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Accepted formats</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • The most recent ~20% of dates (by default) are held out as a BACKTEST —</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  .xlsx (this file), .csv, or .tsv — same columns either way.</t>
+          <t xml:space="preserve">    the model predicts those dates and compares against your real</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    shipped_units to measure accuracy, so include real historical actuals</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    through as recent a date as you have them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • The forecast automatically extends ~8 weeks beyond the LAST date in your</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Shipments sheet — that forward projection has no actuals yet, which is</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  There is no separate "future file" — just include every date you have in</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Shipments, and Price/Weather rows for whatever of those dates you can supply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Minimum size</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  At least ~20 distinct dates of history in Shipments are required to train</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  and backtest. More history (6-12+ months) generally produces a more</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  reliable model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Accepted formats</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  .xlsx (this file, with separate sheets as above), or a single .csv/.tsv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  containing just the Shipments columns (Price/Weather sheets are an xlsx-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  feature — a plain .csv/.tsv always runs without a custom price or weather signal).</t>
         </is>
       </c>
     </row>
@@ -679,15 +796,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,16 +826,6 @@
           <t>shipped_units</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>avg_our_price</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>avg_discount_amt</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -741,12 +846,6 @@
       <c r="D2" t="n">
         <v>42</v>
       </c>
-      <c r="E2" t="n">
-        <v>1580</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-50</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -767,12 +866,6 @@
       <c r="D3" t="n">
         <v>17</v>
       </c>
-      <c r="E3" t="n">
-        <v>990</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -793,12 +886,6 @@
       <c r="D4" t="n">
         <v>39</v>
       </c>
-      <c r="E4" t="n">
-        <v>1580</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -819,11 +906,113 @@
       <c r="D5" t="n">
         <v>21</v>
       </c>
-      <c r="E5" t="n">
-        <v>990</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-30</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ship_day</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>avg_our_price</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>avg_discount_amt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>postal_code</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ship_day</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>temp_mean</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>temp_max</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>temp_min</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>precip_mm</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>is_hot</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>is_cold</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/dashboard/apra_forecast_input_template.xlsx
+++ b/dashboard/apra_forecast_input_template.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Shipments" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Price" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Weather" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Future Price" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Weather" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -85,6 +86,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -464,38 +468,38 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>This workbook has three data sheets: Shipments (required), Price and</t>
+          <t>This workbook has four data sheets: Shipments (required), Price, Future</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Weather (both optional). Fill in what you have and upload the whole file</t>
+          <t>Price, and Weather (all optional except Shipments). Fill in what you have</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>when starting a new scenario run — it replaces the default dataset for</t>
+          <t>and upload the whole file when starting a new scenario run — it replaces</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>that run only.</t>
+          <t>the default dataset for that run only.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -533,12 +537,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Price sheet (optional)</t>
+          <t>Price sheet (optional) — historical price/discount</t>
         </is>
       </c>
     </row>
@@ -592,196 +596,291 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Only covers dates already in Shipments — see "Future Price" below for</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Weather sheet (optional)</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  planned discounts on dates beyond your last Shipments date.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  postal_code, ship_day   Same meaning as in Shipments.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  temp_mean, temp_max, temp_min, precip_mm, is_hot, is_cold</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Future Price sheet (optional) — planned price/discount for the forecast</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Leave this sheet empty and the platform's own default weather data is used</t>
+          <t xml:space="preserve">  ship_day, asin, postal_code   All three required — matched at the full</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  instead (only relevant if the "Weather signal" option is on for the run).</t>
+          <t xml:space="preserve">                                 product x postal_code x day level.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  avg_our_price                 Planned selling price for that date.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Past-looking vs. future-looking data</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  avg_discount_amt               Planned discount for that date.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The Shipments sheet is ONE combined file — the model automatically splits</t>
+          <t xml:space="preserve">  Use this for dates AFTER your last Shipments date — e.g. an upcoming</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  it by date:</t>
+          <t xml:space="preserve">  promotion — so the forward forecast can actually respond to it. Include</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Earlier dates are used to TRAIN the model.</t>
+          <t xml:space="preserve">  either avg_our_price or avg_discount_amt or both; dates you don't specify</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The most recent ~20% of dates (by default) are held out as a BACKTEST —</t>
+          <t xml:space="preserve">  simply carry forward the last known price/discount, same as if this</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    the model predicts those dates and compares against your real</t>
+          <t xml:space="preserve">  sheet were empty.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    shipped_units to measure accuracy, so include real historical actuals</t>
+          <t xml:space="preserve">  Only takes effect when the "Known prices" run option is on (it's on by</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    through as recent a date as you have them.</t>
+          <t xml:space="preserve">  default).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The forecast automatically extends ~8 weeks beyond the LAST date in your</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Shipments sheet — that forward projection has no actuals yet, which is</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Weather sheet (optional)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    expected.</t>
+          <t xml:space="preserve">  postal_code, ship_day   Same meaning as in Shipments.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  There is no separate "future file" — just include every date you have in</t>
+          <t xml:space="preserve">  temp_mean, temp_max, temp_min, precip_mm, is_hot, is_cold</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Shipments, and Price/Weather rows for whatever of those dates you can supply.</t>
+          <t xml:space="preserve">  Leave this sheet empty and the platform's own default weather data is used</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  instead (only relevant if the "Weather signal" option is on for the run).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Minimum size</t>
-        </is>
-      </c>
+      <c r="A43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  At least ~20 distinct dates of history in Shipments are required to train</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Past-looking vs. future-looking data</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  and backtest. More history (6-12+ months) generally produces a more</t>
+          <t xml:space="preserve">  The Shipments sheet is ONE combined file — the model automatically splits</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  reliable model.</t>
+          <t xml:space="preserve">  it by date:</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Earlier dates are used to TRAIN the model.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Accepted formats</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • The most recent ~20% of dates (by default) are held out as a BACKTEST —</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  .xlsx (this file, with separate sheets as above), or a single .csv/.tsv</t>
+          <t xml:space="preserve">    the model predicts those dates and compares against your real</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  containing just the Shipments columns (Price/Weather sheets are an xlsx-only</t>
+          <t xml:space="preserve">    shipped_units to measure accuracy, so include real historical actuals</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  feature — a plain .csv/.tsv always runs without a custom price or weather signal).</t>
+          <t xml:space="preserve">    through as recent a date as you have them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • The forecast automatically extends 52 weeks beyond the LAST date in your</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Shipments sheet — that forward projection has no actuals yet, which is</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    expected. Use the Future Price sheet above to tell the model about any</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    planned discounts within that window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Minimum size</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  At least ~20 distinct dates of history in Shipments are required to train</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  and backtest. More history (6-12+ months) generally produces a more</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  reliable model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Accepted formats</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  .xlsx (this file, with separate sheets as above), or a single .csv/.tsv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  containing just the Shipments columns (Price/Future Price/Weather sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  are an xlsx-only feature — a plain .csv/.tsv always runs without a custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  price, planned-discount, or weather signal).</t>
         </is>
       </c>
     </row>
@@ -960,6 +1059,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>ship_day</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>postal_code</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>avg_our_price</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>avg_discount_amt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SKU-EXAMPLE-001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>135-0061</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SKU-EXAMPLE-001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>135-0061</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E3" t="n">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
